--- a/inadimplentes-clubcasa.xlsx
+++ b/inadimplentes-clubcasa.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09/06/2026 14:09</t>
+          <t>09/06/2026 14:46</t>
         </is>
       </c>
     </row>
